--- a/BAU_Lahan.xlsx
+++ b/BAU_Lahan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{341578DF-EB35-41C1-83E7-14FC778A9539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{341578DF-EB35-41C1-83E7-14FC778A9539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46592FAC-CE32-4273-8DEE-A6C0A7489F8F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{896EBC8B-60CD-4DF5-AF8D-EDFFACB70643}"/>
+    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{896EBC8B-60CD-4DF5-AF8D-EDFFACB70643}"/>
   </bookViews>
   <sheets>
     <sheet name="BAU_Lahan" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -50,82 +50,91 @@
     <t>Hutan lahan kering primer</t>
   </si>
   <si>
-    <t>Hutan sekunder kerapatan tinggi</t>
-  </si>
-  <si>
-    <t>Hutan sekunder kerapatan rendah</t>
-  </si>
-  <si>
-    <t>Hutan rawa primer</t>
-  </si>
-  <si>
-    <t>Hutan rawa sekunder</t>
-  </si>
-  <si>
     <t>Hutan mangrove primer</t>
   </si>
   <si>
     <t>Hutan mangrove sekunder</t>
   </si>
   <si>
-    <t>Tanaman kayu industri</t>
-  </si>
-  <si>
     <t>Kebun campuran</t>
   </si>
   <si>
-    <t>Agroforestri kopi</t>
-  </si>
-  <si>
-    <t>Karet agroforestri</t>
-  </si>
-  <si>
     <t>Karet monokultur</t>
   </si>
   <si>
-    <t>Kelapa sawit skala besar</t>
-  </si>
-  <si>
-    <t>Kelapa sawit skala kecil</t>
-  </si>
-  <si>
-    <t>Kelapa</t>
-  </si>
-  <si>
-    <t>Teh</t>
-  </si>
-  <si>
-    <t>Sawah irigasi</t>
-  </si>
-  <si>
-    <t>Sawah tadah hujan</t>
-  </si>
-  <si>
-    <t>Tebu</t>
-  </si>
-  <si>
-    <t>Tanaman semusim lain</t>
-  </si>
-  <si>
     <t>Semak belukar</t>
   </si>
   <si>
-    <t>Rerumputan</t>
-  </si>
-  <si>
-    <t>Tambang</t>
-  </si>
-  <si>
     <t>Lahan terbuka</t>
   </si>
   <si>
-    <t>Pemukiman</t>
-  </si>
-  <si>
     <t>Tambak</t>
   </si>
   <si>
-    <t>Tubuh air</t>
+    <t>Hutan lahan kering sekunder</t>
+  </si>
+  <si>
+    <t>Hutan kerangas kerapatan tinggi</t>
+  </si>
+  <si>
+    <t>Hutan kerangas kerapatan rendah</t>
+  </si>
+  <si>
+    <t>Hutan Rawa</t>
+  </si>
+  <si>
+    <t>Hutan pantai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jati</t>
+  </si>
+  <si>
+    <t>Kelapa Sawit monokultur</t>
+  </si>
+  <si>
+    <t>Kelapa Monokultur</t>
+  </si>
+  <si>
+    <t>Karet Agroforestri</t>
+  </si>
+  <si>
+    <t>Durian Agroforestri</t>
+  </si>
+  <si>
+    <t>Sawah padi</t>
+  </si>
+  <si>
+    <t>Pertanian lahan kering lainnya</t>
+  </si>
+  <si>
+    <t>Rasau</t>
+  </si>
+  <si>
+    <t>Lada</t>
+  </si>
+  <si>
+    <t>Padang rumput</t>
+  </si>
+  <si>
+    <t>Permukiman</t>
+  </si>
+  <si>
+    <t>Badan air/sungai</t>
+  </si>
+  <si>
+    <t>Lahan terbuka pantai</t>
+  </si>
+  <si>
+    <t>Lamun</t>
+  </si>
+  <si>
+    <t>Terumbu karang</t>
+  </si>
+  <si>
+    <t>Makroalga</t>
+  </si>
+  <si>
+    <t>Substrat terbuka</t>
   </si>
 </sst>
 </file>
@@ -497,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB04FD7-420A-45B0-86D3-235511236A94}">
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -579,67 +588,67 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>281147</v>
+        <v>43334</v>
       </c>
       <c r="D2">
-        <v>274297.9279325183</v>
+        <v>42601.876102874558</v>
       </c>
       <c r="E2">
-        <v>267615.70732774318</v>
+        <v>41882.12137085601</v>
       </c>
       <c r="F2">
-        <v>261096.27348751796</v>
+        <v>41174.526828051014</v>
       </c>
       <c r="G2">
-        <v>254735.6607345207</v>
+        <v>40478.887029194491</v>
       </c>
       <c r="H2">
-        <v>248529.99999999997</v>
+        <v>39794.999999999993</v>
       </c>
       <c r="I2">
-        <v>245591.95083832278</v>
+        <v>39152.377930022209</v>
       </c>
       <c r="J2">
-        <v>242688.63443678088</v>
+        <v>38520.133121630606</v>
       </c>
       <c r="K2">
-        <v>239819.64019481585</v>
+        <v>37898.097999568978</v>
       </c>
       <c r="L2">
-        <v>236984.56236586921</v>
+        <v>37286.107694638602</v>
       </c>
       <c r="M2">
-        <v>234182.99999999997</v>
+        <v>36683.999999999993</v>
       </c>
       <c r="N2">
-        <v>232612.47567671112</v>
+        <v>36136.924235335835</v>
       </c>
       <c r="O2">
-        <v>231052.48391406945</v>
+        <v>35598.007120008791</v>
       </c>
       <c r="P2">
-        <v>229502.95407653489</v>
+        <v>35067.126982463837</v>
       </c>
       <c r="Q2">
-        <v>227963.81600227737</v>
+        <v>34544.163965657965</v>
       </c>
       <c r="R2">
-        <v>226434.99999999997</v>
+        <v>34029.000000000007</v>
       </c>
       <c r="S2">
-        <v>225502.34868177361</v>
+        <v>33584.540300164917</v>
       </c>
       <c r="T2">
-        <v>224573.53881244597</v>
+        <v>33145.88577899443</v>
       </c>
       <c r="U2">
-        <v>223648.55456967346</v>
+        <v>32712.960613867632</v>
       </c>
       <c r="V2">
-        <v>222727.38019628226</v>
+        <v>32285.689972498312</v>
       </c>
       <c r="W2">
-        <v>221810</v>
+        <v>31863.999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -647,70 +656,70 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>268650</v>
+        <v>35802</v>
       </c>
       <c r="D3">
-        <v>267454.20195579919</v>
+        <v>33985.362784813515</v>
       </c>
       <c r="E3">
-        <v>266263.72657291428</v>
+        <v>32260.90396110238</v>
       </c>
       <c r="F3">
-        <v>265078.55015944876</v>
+        <v>30623.946284679394</v>
       </c>
       <c r="G3">
-        <v>263898.64912896202</v>
+        <v>29070.049840441068</v>
       </c>
       <c r="H3">
-        <v>262724</v>
+        <v>27594.999999999996</v>
       </c>
       <c r="I3">
-        <v>261007.72240844849</v>
+        <v>26417.270924778251</v>
       </c>
       <c r="J3">
-        <v>259302.65661624254</v>
+        <v>25289.80623711304</v>
       </c>
       <c r="K3">
-        <v>257608.72938089201</v>
+        <v>24210.460699436924</v>
       </c>
       <c r="L3">
-        <v>255925.86793837254</v>
+        <v>23177.180630937546</v>
       </c>
       <c r="M3">
-        <v>254253.99999999994</v>
+        <v>22188.000000000004</v>
       </c>
       <c r="N3">
-        <v>251996.46482319172</v>
+        <v>21603.172368379535</v>
       </c>
       <c r="O3">
-        <v>249758.97442473314</v>
+        <v>21033.759526677353</v>
       </c>
       <c r="P3">
-        <v>247541.35082594061</v>
+        <v>20479.355174412118</v>
       </c>
       <c r="Q3">
-        <v>245343.41762841295</v>
+        <v>19939.563720303333</v>
       </c>
       <c r="R3">
-        <v>243165</v>
+        <v>19414</v>
       </c>
       <c r="S3">
-        <v>240763.22081065836</v>
+        <v>19078.824746439397</v>
       </c>
       <c r="T3">
-        <v>238385.16437448576</v>
+        <v>18749.436164898958</v>
       </c>
       <c r="U3">
-        <v>236030.59637809472</v>
+        <v>18425.734350708768</v>
       </c>
       <c r="V3">
-        <v>233699.28482244813</v>
+        <v>18107.621124014677</v>
       </c>
       <c r="W3">
-        <v>231391.00000000006</v>
+        <v>17795</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -718,70 +727,70 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>182483</v>
+        <v>51767</v>
       </c>
       <c r="D4">
-        <v>186476.90669536853</v>
+        <v>49041.77888823612</v>
       </c>
       <c r="E4">
-        <v>190558.22586582409</v>
+        <v>46460.024272657138</v>
       </c>
       <c r="F4">
-        <v>194728.87066091769</v>
+        <v>44014.183505355431</v>
       </c>
       <c r="G4">
-        <v>198990.79610226944</v>
+        <v>41697.10153989782</v>
       </c>
       <c r="H4">
-        <v>203346</v>
+        <v>39501.999999999978</v>
       </c>
       <c r="I4">
-        <v>206945.3062658108</v>
+        <v>37595.184687081513</v>
       </c>
       <c r="J4">
-        <v>210608.3217051244</v>
+        <v>35780.413945009575</v>
       </c>
       <c r="K4">
-        <v>214336.1739960234</v>
+        <v>34053.244657051837</v>
       </c>
       <c r="L4">
-        <v>218130.01077694751</v>
+        <v>32409.448181768912</v>
       </c>
       <c r="M4">
-        <v>221991.00000000006</v>
+        <v>30845.000000000007</v>
       </c>
       <c r="N4">
-        <v>224372.932960101</v>
+        <v>29573.150611013341</v>
       </c>
       <c r="O4">
-        <v>226780.42373392606</v>
+        <v>28353.744109634586</v>
       </c>
       <c r="P4">
-        <v>229213.74655330842</v>
+        <v>27184.618088518593</v>
       </c>
       <c r="Q4">
-        <v>231673.17859255127</v>
+        <v>26063.699304089416</v>
       </c>
       <c r="R4">
-        <v>234159.00000000006</v>
+        <v>24989</v>
       </c>
       <c r="S4">
-        <v>236164.35650972882</v>
+        <v>24120.951592842135</v>
       </c>
       <c r="T4">
-        <v>238186.88705390051</v>
+        <v>23283.056774750232</v>
       </c>
       <c r="U4">
-        <v>240226.73871232741</v>
+        <v>22474.268093847113</v>
       </c>
       <c r="V4">
-        <v>242284.05982442512</v>
+        <v>21693.574483822591</v>
       </c>
       <c r="W4">
-        <v>244358.99999999997</v>
+        <v>20940.000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -789,70 +798,70 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>34376</v>
+        <v>15244</v>
       </c>
       <c r="D5">
-        <v>34072.487570670695</v>
+        <v>15273.088772907869</v>
       </c>
       <c r="E5">
-        <v>33771.654911959187</v>
+        <v>15302.23305334062</v>
       </c>
       <c r="F5">
-        <v>33473.47836364642</v>
+        <v>15331.432947218338</v>
       </c>
       <c r="G5">
-        <v>33177.934474414047</v>
+        <v>15360.688560663226</v>
       </c>
       <c r="H5">
-        <v>32884.999999999985</v>
+        <v>15389.999999999991</v>
       </c>
       <c r="I5">
-        <v>32683.546874929587</v>
+        <v>15377.981242655738</v>
       </c>
       <c r="J5">
-        <v>32483.327849345282</v>
+        <v>15365.971871310703</v>
       </c>
       <c r="K5">
-        <v>32284.335363168077</v>
+        <v>15353.971878634939</v>
       </c>
       <c r="L5">
-        <v>32086.561902631922</v>
+        <v>15341.981257304209</v>
       </c>
       <c r="M5">
-        <v>31890.000000000007</v>
+        <v>15330.000000000002</v>
       </c>
       <c r="N5">
-        <v>31739.180163060457</v>
+        <v>15326.598490841807</v>
       </c>
       <c r="O5">
-        <v>31589.073610009735</v>
+        <v>15323.19773643016</v>
       </c>
       <c r="P5">
-        <v>31439.676967459316</v>
+        <v>15319.797736597591</v>
       </c>
       <c r="Q5">
-        <v>31290.986877974712</v>
+        <v>15316.398491176671</v>
       </c>
       <c r="R5">
-        <v>31143.000000000004</v>
+        <v>15313.000000000005</v>
       </c>
       <c r="S5">
-        <v>31010.476936194562</v>
+        <v>15295.158473269763</v>
       </c>
       <c r="T5">
-        <v>30878.517798871493</v>
+        <v>15277.337734110613</v>
       </c>
       <c r="U5">
-        <v>30747.120188349796</v>
+        <v>15259.537758302477</v>
       </c>
       <c r="V5">
-        <v>30616.281715159861</v>
+        <v>15241.758521653497</v>
       </c>
       <c r="W5">
-        <v>30486.000000000004</v>
+        <v>15224.000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -860,70 +869,70 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>436939</v>
+        <v>5351</v>
       </c>
       <c r="D6">
-        <v>436501.72565556091</v>
+        <v>5042.652940649542</v>
       </c>
       <c r="E6">
-        <v>436064.88892106811</v>
+        <v>4752.0741319083299</v>
       </c>
       <c r="F6">
-        <v>435628.48935857572</v>
+        <v>4478.2396926653255</v>
       </c>
       <c r="G6">
-        <v>435192.52653057629</v>
+        <v>4220.184742132742</v>
       </c>
       <c r="H6">
-        <v>434757.00000000006</v>
+        <v>3977</v>
       </c>
       <c r="I6">
-        <v>434322.53251100302</v>
+        <v>3778.0697544968248</v>
       </c>
       <c r="J6">
-        <v>433888.4992001768</v>
+        <v>3589.0900351631126</v>
       </c>
       <c r="K6">
-        <v>433454.89963363233</v>
+        <v>3409.5631149146848</v>
       </c>
       <c r="L6">
-        <v>433021.73337791418</v>
+        <v>3239.0161630644084</v>
       </c>
       <c r="M6">
-        <v>432589</v>
+        <v>3076.9999999999991</v>
       </c>
       <c r="N6">
-        <v>432158.54418572242</v>
+        <v>2988.6724783304303</v>
       </c>
       <c r="O6">
-        <v>431728.51670459256</v>
+        <v>2902.8804623756114</v>
       </c>
       <c r="P6">
-        <v>431298.91713038948</v>
+        <v>2819.5511686009436</v>
       </c>
       <c r="Q6">
-        <v>430869.74503731634</v>
+        <v>2738.6139027760942</v>
       </c>
       <c r="R6">
-        <v>430441.00000000006</v>
+        <v>2660.0000000000005</v>
       </c>
       <c r="S6">
-        <v>430012.54790381651</v>
+        <v>2606.4900024228073</v>
       </c>
       <c r="T6">
-        <v>429584.52228001534</v>
+        <v>2554.0564408759569</v>
       </c>
       <c r="U6">
-        <v>429156.92270409473</v>
+        <v>2502.6776611905111</v>
       </c>
       <c r="V6">
-        <v>428729.74875197536</v>
+        <v>2452.3324448044964</v>
       </c>
       <c r="W6">
-        <v>428303.00000000006</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -931,70 +940,70 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>99848</v>
+        <v>9489</v>
       </c>
       <c r="D7">
-        <v>99887.568626376582</v>
+        <v>9285.4527947134738</v>
       </c>
       <c r="E7">
-        <v>99927.1529333496</v>
+        <v>9086.271851918249</v>
       </c>
       <c r="F7">
-        <v>99966.7529271331</v>
+        <v>8891.3635115313173</v>
       </c>
       <c r="G7">
-        <v>100006.36861394359</v>
+        <v>8700.6361225589499</v>
       </c>
       <c r="H7">
-        <v>100046.00000000003</v>
+        <v>8514</v>
       </c>
       <c r="I7">
-        <v>99708.936446931722</v>
+        <v>8350.4349866464017</v>
       </c>
       <c r="J7">
-        <v>99373.008489877349</v>
+        <v>8190.0122699328513</v>
       </c>
       <c r="K7">
-        <v>99038.212302916538</v>
+        <v>8032.6714822540052</v>
       </c>
       <c r="L7">
-        <v>98704.544073018784</v>
+        <v>7878.3534157447339</v>
       </c>
       <c r="M7">
-        <v>98372.000000000015</v>
+        <v>7727.0000000000018</v>
       </c>
       <c r="N7">
-        <v>98085.334115293241</v>
+        <v>7603.302475774547</v>
       </c>
       <c r="O7">
-        <v>97799.503603756224</v>
+        <v>7481.5851608799476</v>
       </c>
       <c r="P7">
-        <v>97514.506031027675</v>
+        <v>7361.8163551749212</v>
       </c>
       <c r="Q7">
-        <v>97230.338969840275</v>
+        <v>7243.9648659892628</v>
       </c>
       <c r="R7">
-        <v>96947</v>
+        <v>7128</v>
       </c>
       <c r="S7">
-        <v>96687.009257562924</v>
+        <v>7023.3732749792407</v>
       </c>
       <c r="T7">
-        <v>96427.715753680444</v>
+        <v>6920.2822895191675</v>
       </c>
       <c r="U7">
-        <v>96169.117618510601</v>
+        <v>6818.7045016163129</v>
       </c>
       <c r="V7">
-        <v>95911.212987225925</v>
+        <v>6718.6177001448732</v>
       </c>
       <c r="W7">
-        <v>95654.000000000029</v>
+        <v>6619.9999999999991</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -1002,70 +1011,70 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>109515</v>
+        <v>11866</v>
       </c>
       <c r="D8">
-        <v>106205.76036170039</v>
+        <v>11744.121914991618</v>
       </c>
       <c r="E8">
-        <v>102996.5167694556</v>
+        <v>11623.495664435057</v>
       </c>
       <c r="F8">
-        <v>99884.247620021517</v>
+        <v>11504.108390485573</v>
       </c>
       <c r="G8">
-        <v>96866.022614625821</v>
+        <v>11385.947367363944</v>
       </c>
       <c r="H8">
-        <v>93939</v>
+        <v>11269</v>
       </c>
       <c r="I8">
-        <v>92184.688726474022</v>
+        <v>11159.7002344054</v>
       </c>
       <c r="J8">
-        <v>90463.139224357379</v>
+        <v>11051.4605840614</v>
       </c>
       <c r="K8">
-        <v>88773.739667412563</v>
+        <v>10944.270766747009</v>
       </c>
       <c r="L8">
-        <v>87115.889655259976</v>
+        <v>10838.120599970074</v>
       </c>
       <c r="M8">
-        <v>85489</v>
+        <v>10733.000000000002</v>
       </c>
       <c r="N8">
-        <v>84123.040809591781</v>
+        <v>10637.516143085304</v>
       </c>
       <c r="O8">
-        <v>82778.907169954546</v>
+        <v>10542.881738041595</v>
       </c>
       <c r="P8">
-        <v>81456.250348366404</v>
+        <v>10449.08922790056</v>
       </c>
       <c r="Q8">
-        <v>80154.727184221963</v>
+        <v>10356.131122922852</v>
       </c>
       <c r="R8">
-        <v>78874</v>
+        <v>10263.999999999998</v>
       </c>
       <c r="S8">
-        <v>77743.45156743344</v>
+        <v>10178.383536794627</v>
       </c>
       <c r="T8">
-        <v>76629.107964828319</v>
+        <v>10093.481237538181</v>
       </c>
       <c r="U8">
-        <v>75530.736918620314</v>
+        <v>10009.287145080287</v>
       </c>
       <c r="V8">
-        <v>74448.109484561646</v>
+        <v>9925.7953519617386</v>
       </c>
       <c r="W8">
-        <v>73381.000000000015</v>
+        <v>9842.9999999999982</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -1073,70 +1082,70 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>417121</v>
+        <v>8339</v>
       </c>
       <c r="D9">
-        <v>422920.66449729213</v>
+        <v>8378.4254391586601</v>
       </c>
       <c r="E9">
-        <v>428800.96772598627</v>
+        <v>8418.037275397648</v>
       </c>
       <c r="F9">
-        <v>434763.0308897323</v>
+        <v>8457.8363899721207</v>
       </c>
       <c r="G9">
-        <v>440807.99078143347</v>
+        <v>8497.8236683036648</v>
       </c>
       <c r="H9">
-        <v>446937.00000000012</v>
+        <v>8537.9999999999982</v>
       </c>
       <c r="I9">
-        <v>447494.00988495181</v>
+        <v>8571.3386244249468</v>
       </c>
       <c r="J9">
-        <v>448051.7139617292</v>
+        <v>8604.8074273318034</v>
       </c>
       <c r="K9">
-        <v>448610.11309549143</v>
+        <v>8638.4069170330004</v>
       </c>
       <c r="L9">
-        <v>449169.20815247606</v>
+        <v>8672.1376038257895</v>
       </c>
       <c r="M9">
-        <v>449729.00000000023</v>
+        <v>8706</v>
       </c>
       <c r="N9">
-        <v>448782.02034041565</v>
+        <v>8749.9539336668477</v>
       </c>
       <c r="O9">
-        <v>447837.03470495617</v>
+        <v>8794.1297773135702</v>
       </c>
       <c r="P9">
-        <v>446894.03889487014</v>
+        <v>8838.5286512958464</v>
       </c>
       <c r="Q9">
-        <v>445953.02872024733</v>
+        <v>8883.1516816256881</v>
       </c>
       <c r="R9">
-        <v>445014</v>
+        <v>8927.9999999999964</v>
       </c>
       <c r="S9">
-        <v>442916.92855693673</v>
+        <v>8986.2353168922909</v>
       </c>
       <c r="T9">
-        <v>440829.73929429322</v>
+        <v>9044.8504895343067</v>
       </c>
       <c r="U9">
-        <v>438752.38564356067</v>
+        <v>9103.8479956388564</v>
       </c>
       <c r="V9">
-        <v>436684.82125567849</v>
+        <v>9163.2303290803065</v>
       </c>
       <c r="W9">
-        <v>434627.00000000006</v>
+        <v>9223.0000000000018</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -1144,70 +1153,70 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>204935</v>
+        <v>2444</v>
       </c>
       <c r="D10">
-        <v>200761.21776861668</v>
+        <v>2393.1256266899063</v>
       </c>
       <c r="E10">
-        <v>196672.44033443742</v>
+        <v>2343.3102557773964</v>
       </c>
       <c r="F10">
-        <v>192666.93645822949</v>
+        <v>2294.5318430385296</v>
       </c>
       <c r="G10">
-        <v>188743.01015982067</v>
+        <v>2246.7688031225562</v>
       </c>
       <c r="H10">
-        <v>184898.99999999994</v>
+        <v>2199.9999999999991</v>
       </c>
       <c r="I10">
-        <v>184945.1769296597</v>
+        <v>2214.0201621698616</v>
       </c>
       <c r="J10">
-        <v>184991.36539160908</v>
+        <v>2228.1296720430273</v>
       </c>
       <c r="K10">
-        <v>185037.56538872825</v>
+        <v>2242.3290990146288</v>
       </c>
       <c r="L10">
-        <v>185083.77692389803</v>
+        <v>2256.6190161084401</v>
       </c>
       <c r="M10">
-        <v>185129.99999999991</v>
+        <v>2271.0000000000009</v>
       </c>
       <c r="N10">
-        <v>185617.22864637233</v>
+        <v>2297.952606074191</v>
       </c>
       <c r="O10">
-        <v>186105.73959034009</v>
+        <v>2325.2250901643179</v>
       </c>
       <c r="P10">
-        <v>186595.53620667846</v>
+        <v>2352.8212486359271</v>
       </c>
       <c r="Q10">
-        <v>187086.62187904434</v>
+        <v>2380.7449229104627</v>
       </c>
       <c r="R10">
-        <v>187578.99999999985</v>
+        <v>2408.9999999999986</v>
       </c>
       <c r="S10">
-        <v>187807.04484496696</v>
+        <v>2440.7518819596071</v>
       </c>
       <c r="T10">
-        <v>188035.36693019705</v>
+        <v>2472.9222703567302</v>
       </c>
       <c r="U10">
-        <v>188263.96659273873</v>
+        <v>2505.5166813254518</v>
       </c>
       <c r="V10">
-        <v>188492.8441700502</v>
+        <v>2538.5407037053906</v>
       </c>
       <c r="W10">
-        <v>188721.99999999994</v>
+        <v>2571.9999999999986</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -1215,70 +1224,70 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>532082</v>
+        <v>8545</v>
       </c>
       <c r="D11">
-        <v>538117.32272265281</v>
+        <v>8722.8417089173836</v>
       </c>
       <c r="E11">
-        <v>544221.10316491756</v>
+        <v>8904.3847254334396</v>
       </c>
       <c r="F11">
-        <v>550394.11783197708</v>
+        <v>9089.7060825345434</v>
       </c>
       <c r="G11">
-        <v>556637.15203679097</v>
+        <v>9278.8844164461498</v>
       </c>
       <c r="H11">
-        <v>562951.00000000035</v>
+        <v>9472.0000000000018</v>
       </c>
       <c r="I11">
-        <v>567427.63442110526</v>
+        <v>9630.2248310804771</v>
       </c>
       <c r="J11">
-        <v>571939.86742137675</v>
+        <v>9791.0927256291179</v>
       </c>
       <c r="K11">
-        <v>576487.98208375566</v>
+        <v>9954.6478346457934</v>
       </c>
       <c r="L11">
-        <v>581072.26374228299</v>
+        <v>10120.935046649854</v>
       </c>
       <c r="M11">
-        <v>585693.00000000035</v>
+        <v>10290.000000000007</v>
       </c>
       <c r="N11">
-        <v>589230.02084099536</v>
+        <v>10422.731326525831</v>
       </c>
       <c r="O11">
-        <v>592788.40187654598</v>
+        <v>10557.174762385122</v>
       </c>
       <c r="P11">
-        <v>596368.2721016258</v>
+        <v>10693.352392178747</v>
       </c>
       <c r="Q11">
-        <v>599969.76129021414</v>
+        <v>10831.28658537817</v>
       </c>
       <c r="R11">
-        <v>603592.99999999988</v>
+        <v>10971.000000000004</v>
       </c>
       <c r="S11">
-        <v>606310.42151863489</v>
+        <v>11074.045997314995</v>
       </c>
       <c r="T11">
-        <v>609040.07707528863</v>
+        <v>11178.059862423504</v>
       </c>
       <c r="U11">
-        <v>611782.0217485294</v>
+        <v>11283.050686101396</v>
       </c>
       <c r="V11">
-        <v>614536.31086489325</v>
+        <v>11389.027644510381</v>
       </c>
       <c r="W11">
-        <v>617303.00000000047</v>
+        <v>11496.000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -1286,70 +1295,70 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>341390</v>
+        <v>76675</v>
       </c>
       <c r="D12">
-        <v>332571.86961048708</v>
+        <v>78723.570380748075</v>
       </c>
       <c r="E12">
-        <v>323981.51221832749</v>
+        <v>80826.873602772685</v>
       </c>
       <c r="F12">
-        <v>315613.04442919255</v>
+        <v>82986.371995092326</v>
       </c>
       <c r="G12">
-        <v>307460.73481728899</v>
+        <v>85203.566956616778</v>
       </c>
       <c r="H12">
-        <v>299518.99999999994</v>
+        <v>87480.000000000029</v>
       </c>
       <c r="I12">
-        <v>294849.66741271038</v>
+        <v>88561.906105629489</v>
       </c>
       <c r="J12">
-        <v>290253.12709172349</v>
+        <v>89657.19265046106</v>
       </c>
       <c r="K12">
-        <v>285728.24424658815</v>
+        <v>90766.025116649136</v>
       </c>
       <c r="L12">
-        <v>281273.90177759744</v>
+        <v>91888.571032943408</v>
       </c>
       <c r="M12">
-        <v>276888.99999999994</v>
+        <v>93025</v>
       </c>
       <c r="N12">
-        <v>275599.24033773778</v>
+        <v>93575.837800767986</v>
       </c>
       <c r="O12">
-        <v>274315.48842582462</v>
+        <v>94129.937329918175</v>
       </c>
       <c r="P12">
-        <v>273037.71627992723</v>
+        <v>94687.317901433795</v>
       </c>
       <c r="Q12">
-        <v>271765.89604606444</v>
+        <v>95247.998943663784</v>
       </c>
       <c r="R12">
-        <v>270499.99999999994</v>
+        <v>95812.000000000029</v>
       </c>
       <c r="S12">
-        <v>269682.06845002429</v>
+        <v>95802.398075654157</v>
       </c>
       <c r="T12">
-        <v>268866.6101422683</v>
+        <v>95792.797113577661</v>
       </c>
       <c r="U12">
-        <v>268053.61759820033</v>
+        <v>95783.197113674076</v>
       </c>
       <c r="V12">
-        <v>267243.08336190198</v>
+        <v>95773.598075846996</v>
       </c>
       <c r="W12">
-        <v>266435</v>
+        <v>95763.999999999985</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -1357,70 +1366,70 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>1483502</v>
+        <v>14084</v>
       </c>
       <c r="D13">
-        <v>1483589.389703539</v>
+        <v>14143.691869805336</v>
       </c>
       <c r="E13">
-        <v>1483676.7845550051</v>
+        <v>14203.636730190114</v>
       </c>
       <c r="F13">
-        <v>1483764.1845547017</v>
+        <v>14263.835653398064</v>
       </c>
       <c r="G13">
-        <v>1483851.5897029319</v>
+        <v>14324.289716217387</v>
       </c>
       <c r="H13">
-        <v>1483938.9999999993</v>
+        <v>14385.000000000002</v>
       </c>
       <c r="I13">
-        <v>1475961.6915491384</v>
+        <v>14459.034019128192</v>
       </c>
       <c r="J13">
-        <v>1468027.2672398218</v>
+        <v>14533.449062655987</v>
       </c>
       <c r="K13">
-        <v>1460135.4965369508</v>
+        <v>14608.247091568277</v>
       </c>
       <c r="L13">
-        <v>1452286.1501447288</v>
+        <v>14683.430076942384</v>
       </c>
       <c r="M13">
-        <v>1444478.9999999998</v>
+        <v>14759.000000000002</v>
       </c>
       <c r="N13">
-        <v>1435812.2219390133</v>
+        <v>14827.756390557191</v>
       </c>
       <c r="O13">
-        <v>1427197.443970765</v>
+        <v>14896.833090162589</v>
       </c>
       <c r="P13">
-        <v>1418634.3540981521</v>
+        <v>14966.231591010379</v>
       </c>
       <c r="Q13">
-        <v>1410122.6421960341</v>
+        <v>15035.953392246296</v>
       </c>
       <c r="R13">
-        <v>1401662</v>
+        <v>15106.000000000007</v>
       </c>
       <c r="S13">
-        <v>1393944.4816863544</v>
+        <v>15194.164843268145</v>
       </c>
       <c r="T13">
-        <v>1386269.4558487274</v>
+        <v>15282.844252906507</v>
       </c>
       <c r="U13">
-        <v>1378636.6885245363</v>
+        <v>15372.041232136547</v>
       </c>
       <c r="V13">
-        <v>1371045.9470393909</v>
+        <v>15461.758801707763</v>
       </c>
       <c r="W13">
-        <v>1363497.0000000005</v>
+        <v>15551.999999999995</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -1428,70 +1437,70 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>1014499</v>
+        <v>29949</v>
       </c>
       <c r="D14">
-        <v>1019903.1182711354</v>
+        <v>30573.414316540915</v>
       </c>
       <c r="E14">
-        <v>1025336.0236522516</v>
+        <v>31210.847205945742</v>
       </c>
       <c r="F14">
-        <v>1030797.8694889379</v>
+        <v>31861.570095750529</v>
       </c>
       <c r="G14">
-        <v>1036288.8099436378</v>
+        <v>32525.860072553045</v>
       </c>
       <c r="H14">
-        <v>1041809.0000000001</v>
+        <v>33203.999999999993</v>
       </c>
       <c r="I14">
-        <v>1046655.4979051016</v>
+        <v>33766.795526869639</v>
       </c>
       <c r="J14">
-        <v>1051524.5417297953</v>
+        <v>34339.130229894698</v>
       </c>
       <c r="K14">
-        <v>1056416.2363577515</v>
+        <v>34921.16579458506</v>
       </c>
       <c r="L14">
-        <v>1061330.6871605602</v>
+        <v>35513.066646960244</v>
       </c>
       <c r="M14">
-        <v>1066267.9999999998</v>
+        <v>36115.000000000015</v>
       </c>
       <c r="N14">
-        <v>1069853.4063862897</v>
+        <v>36364.917110605915</v>
       </c>
       <c r="O14">
-        <v>1073450.8689713541</v>
+        <v>36616.56365668666</v>
       </c>
       <c r="P14">
-        <v>1077060.4282950684</v>
+        <v>36869.951605998489</v>
       </c>
       <c r="Q14">
-        <v>1080682.1250336268</v>
+        <v>37125.093009114949</v>
       </c>
       <c r="R14">
-        <v>1084316</v>
+        <v>37382.000000000007</v>
       </c>
       <c r="S14">
-        <v>1087261.1575461703</v>
+        <v>37381.399980738468</v>
       </c>
       <c r="T14">
-        <v>1090214.3145620264</v>
+        <v>37380.799971107852</v>
       </c>
       <c r="U14">
-        <v>1093175.4927752735</v>
+        <v>37380.199971108006</v>
       </c>
       <c r="V14">
-        <v>1096144.7139726325</v>
+        <v>37379.599980738771</v>
       </c>
       <c r="W14">
-        <v>1099122.0000000002</v>
+        <v>37378.999999999993</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -1499,70 +1508,70 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>662075</v>
+        <v>3626</v>
       </c>
       <c r="D15">
-        <v>657940.27804117755</v>
+        <v>3723.6022658806069</v>
       </c>
       <c r="E15">
-        <v>653831.37781807501</v>
+        <v>3823.8317248955295</v>
       </c>
       <c r="F15">
-        <v>649748.13807147299</v>
+        <v>3926.7590940891187</v>
       </c>
       <c r="G15">
-        <v>645690.39854923135</v>
+        <v>4032.4569940202764</v>
       </c>
       <c r="H15">
-        <v>641658</v>
+        <v>4141.0000000000009</v>
       </c>
       <c r="I15">
-        <v>638970.37960950111</v>
+        <v>4226.5881631182692</v>
       </c>
       <c r="J15">
-        <v>636294.01646719896</v>
+        <v>4313.945303214553</v>
       </c>
       <c r="K15">
-        <v>633628.8634214804</v>
+        <v>4403.1079823487762</v>
       </c>
       <c r="L15">
-        <v>630974.87351822946</v>
+        <v>4494.1135182629559</v>
       </c>
       <c r="M15">
-        <v>628332</v>
+        <v>4587.0000000000018</v>
       </c>
       <c r="N15">
-        <v>626222.68549778056</v>
+        <v>4646.6293925997843</v>
       </c>
       <c r="O15">
-        <v>624120.45197769988</v>
+        <v>4707.033946407726</v>
       </c>
       <c r="P15">
-        <v>622025.27566885622</v>
+        <v>4768.2237382478961</v>
       </c>
       <c r="Q15">
-        <v>619937.13288014673</v>
+        <v>4830.2089759395458</v>
       </c>
       <c r="R15">
-        <v>617855.99999999988</v>
+        <v>4893</v>
       </c>
       <c r="S15">
-        <v>615865.61747123394</v>
+        <v>4961.0790156904859</v>
       </c>
       <c r="T15">
-        <v>613881.64682907378</v>
+        <v>5030.1052523859562</v>
       </c>
       <c r="U15">
-        <v>611904.06741804804</v>
+        <v>5100.0918892962318</v>
       </c>
       <c r="V15">
-        <v>609932.85864922521</v>
+        <v>5171.0522890007724</v>
       </c>
       <c r="W15">
-        <v>607967.99999999988</v>
+        <v>5242.9999999999973</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -1570,70 +1579,70 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C16">
-        <v>91437</v>
+        <v>19402</v>
       </c>
       <c r="D16">
-        <v>90300.707235282651</v>
+        <v>19447.189010583446</v>
       </c>
       <c r="E16">
-        <v>89178.535244947096</v>
+        <v>19492.483270454468</v>
       </c>
       <c r="F16">
-        <v>88070.30854933236</v>
+        <v>19537.88302474816</v>
       </c>
       <c r="G16">
-        <v>86975.853849473104</v>
+        <v>19583.388519170567</v>
       </c>
       <c r="H16">
-        <v>85895.000000000015</v>
+        <v>19628.999999999996</v>
       </c>
       <c r="I16">
-        <v>85417.92995535463</v>
+        <v>19856.657639495224</v>
       </c>
       <c r="J16">
-        <v>84943.509608916356</v>
+        <v>20086.955658063278</v>
       </c>
       <c r="K16">
-        <v>84471.724243977078</v>
+        <v>20319.924678887564</v>
       </c>
       <c r="L16">
-        <v>84002.559225566874</v>
+        <v>20555.595680319951</v>
       </c>
       <c r="M16">
-        <v>83536.000000000015</v>
+        <v>20794.000000000011</v>
       </c>
       <c r="N16">
-        <v>83383.443810401528</v>
+        <v>21005.839558733544</v>
       </c>
       <c r="O16">
-        <v>83231.166223932072</v>
+        <v>21219.837239937242</v>
       </c>
       <c r="P16">
-        <v>83079.166731797435</v>
+        <v>21436.015029554725</v>
       </c>
       <c r="Q16">
-        <v>82927.444826132589</v>
+        <v>21654.39513751214</v>
       </c>
       <c r="R16">
-        <v>82776</v>
+        <v>21874.999999999989</v>
       </c>
       <c r="S16">
-        <v>82750.784642393788</v>
+        <v>22056.560993473951</v>
       </c>
       <c r="T16">
-        <v>82725.576965930159</v>
+        <v>22239.628930689676</v>
       </c>
       <c r="U16">
-        <v>82700.37696826928</v>
+        <v>22424.216319176445</v>
       </c>
       <c r="V16">
-        <v>82675.184647072019</v>
+        <v>22610.335770275164</v>
       </c>
       <c r="W16">
-        <v>82649.999999999971</v>
+        <v>22798</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -1641,70 +1650,70 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>57076</v>
+        <v>6126</v>
       </c>
       <c r="D17">
-        <v>57101.177776993638</v>
+        <v>6423.8036082910312</v>
       </c>
       <c r="E17">
-        <v>57126.366660589956</v>
+        <v>6736.0843613928946</v>
       </c>
       <c r="F17">
-        <v>57151.566655688373</v>
+        <v>7063.5460376213623</v>
       </c>
       <c r="G17">
-        <v>57176.777767190477</v>
+        <v>7406.9266281100108</v>
       </c>
       <c r="H17">
-        <v>57202.000000000015</v>
+        <v>7767.0000000000018</v>
       </c>
       <c r="I17">
-        <v>57425.644371191869</v>
+        <v>7995.0137115979269</v>
       </c>
       <c r="J17">
-        <v>57650.16313147443</v>
+        <v>8229.7211598608028</v>
       </c>
       <c r="K17">
-        <v>57875.559699472884</v>
+        <v>8471.3188509997053</v>
       </c>
       <c r="L17">
-        <v>58101.837507178316</v>
+        <v>8720.0090600052317</v>
       </c>
       <c r="M17">
-        <v>58328.999999999985</v>
+        <v>8975.9999999999964</v>
       </c>
       <c r="N17">
-        <v>58565.868373100646</v>
+        <v>9112.7681122571012</v>
       </c>
       <c r="O17">
-        <v>58803.698645533965</v>
+        <v>9251.6201724342536</v>
       </c>
       <c r="P17">
-        <v>59042.494723479213</v>
+        <v>9392.5879338317081</v>
       </c>
       <c r="Q17">
-        <v>59282.260528978259</v>
+        <v>9535.7036335775847</v>
       </c>
       <c r="R17">
-        <v>59523.000000000007</v>
+        <v>9680.9999999999982</v>
       </c>
       <c r="S17">
-        <v>59778.595468200125</v>
+        <v>9769.9503367385514</v>
       </c>
       <c r="T17">
-        <v>60035.28847925536</v>
+        <v>9859.7179611959236</v>
       </c>
       <c r="U17">
-        <v>60293.083746083059</v>
+        <v>9950.3103827221639</v>
       </c>
       <c r="V17">
-        <v>60551.986001838137</v>
+        <v>10041.735179664242</v>
       </c>
       <c r="W17">
-        <v>60811.999999999978</v>
+        <v>10134.000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -1712,70 +1721,70 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C18">
-        <v>393253</v>
+        <v>17116</v>
       </c>
       <c r="D18">
-        <v>389781.23920138658</v>
+        <v>17447.507411195937</v>
       </c>
       <c r="E18">
-        <v>386340.12819576339</v>
+        <v>17785.435549412079</v>
       </c>
       <c r="F18">
-        <v>382929.39639714686</v>
+        <v>18129.908773061165</v>
       </c>
       <c r="G18">
-        <v>379548.77560837136</v>
+        <v>18481.053849163993</v>
       </c>
       <c r="H18">
-        <v>376197.99999999994</v>
+        <v>18838.999999999996</v>
       </c>
       <c r="I18">
-        <v>373711.54850513971</v>
+        <v>19132.134607000386</v>
       </c>
       <c r="J18">
-        <v>371241.53101853118</v>
+        <v>19429.830384860226</v>
       </c>
       <c r="K18">
-        <v>368787.83892087184</v>
+        <v>19732.158305341683</v>
       </c>
       <c r="L18">
-        <v>366350.36431077</v>
+        <v>20039.190444526659</v>
       </c>
       <c r="M18">
-        <v>363928.99999999983</v>
+        <v>20350.999999999996</v>
       </c>
       <c r="N18">
-        <v>361963.07477761159</v>
+        <v>20629.473975371839</v>
       </c>
       <c r="O18">
-        <v>360007.76937936473</v>
+        <v>20911.758463984275</v>
       </c>
       <c r="P18">
-        <v>358063.02643753082</v>
+        <v>21197.905607195</v>
       </c>
       <c r="Q18">
-        <v>356128.78889427852</v>
+        <v>21487.968259840698</v>
       </c>
       <c r="R18">
-        <v>354204.99999999994</v>
+        <v>21781.999999999989</v>
       </c>
       <c r="S18">
-        <v>352607.04695417022</v>
+        <v>22050.688971963147</v>
       </c>
       <c r="T18">
-        <v>351016.30288036703</v>
+        <v>22322.692321102615</v>
       </c>
       <c r="U18">
-        <v>349432.73525618447</v>
+        <v>22598.050931478461</v>
       </c>
       <c r="V18">
-        <v>347856.31170593743</v>
+        <v>22876.806191470645</v>
       </c>
       <c r="W18">
-        <v>346286.99999999988</v>
+        <v>23159</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -1783,70 +1792,70 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>265014</v>
+        <v>1346</v>
       </c>
       <c r="D19">
-        <v>274274.58696171793</v>
+        <v>1339.5382553106715</v>
       </c>
       <c r="E19">
-        <v>283858.77369882714</v>
+        <v>1333.1075315310236</v>
       </c>
       <c r="F19">
-        <v>293777.86800586228</v>
+        <v>1326.7076797389177</v>
       </c>
       <c r="G19">
-        <v>304043.57281427388</v>
+        <v>1320.3385517271463</v>
       </c>
       <c r="H19">
-        <v>314667.99999999994</v>
+        <v>1314.0000000000002</v>
       </c>
       <c r="I19">
-        <v>319245.28291827405</v>
+        <v>1307.9444426615075</v>
       </c>
       <c r="J19">
-        <v>323889.14877130452</v>
+        <v>1301.9167923052676</v>
       </c>
       <c r="K19">
-        <v>328600.56610031548</v>
+        <v>1295.9169203222002</v>
       </c>
       <c r="L19">
-        <v>333380.51753530779</v>
+        <v>1289.944698695919</v>
       </c>
       <c r="M19">
-        <v>338229.99999999988</v>
+        <v>1284</v>
       </c>
       <c r="N19">
-        <v>341307.09953795874</v>
+        <v>1279.1637043269216</v>
       </c>
       <c r="O19">
-        <v>344412.19346306974</v>
+        <v>1274.3456249745886</v>
       </c>
       <c r="P19">
-        <v>347545.53645858332</v>
+        <v>1269.5456933296734</v>
       </c>
       <c r="Q19">
-        <v>350707.38552477001</v>
+        <v>1264.7638410372858</v>
       </c>
       <c r="R19">
-        <v>353897.99999999983</v>
+        <v>1260.0000000000002</v>
       </c>
       <c r="S19">
-        <v>356099.24564733222</v>
+        <v>1257.1874719418272</v>
       </c>
       <c r="T19">
-        <v>358314.18304313405</v>
+        <v>1254.3812219107006</v>
       </c>
       <c r="U19">
-        <v>360542.89735008433</v>
+        <v>1251.5812358930268</v>
       </c>
       <c r="V19">
-        <v>362785.47426057386</v>
+        <v>1248.7874999064938</v>
       </c>
       <c r="W19">
-        <v>365042</v>
+        <v>1245.9999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -1854,70 +1863,70 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>279198</v>
+        <v>42496</v>
       </c>
       <c r="D20">
-        <v>281702.84998588677</v>
+        <v>43142.0554650337</v>
       </c>
       <c r="E20">
-        <v>284230.17245886795</v>
+        <v>43797.932740682518</v>
       </c>
       <c r="F20">
-        <v>286780.16903288418</v>
+        <v>44463.781145339344</v>
       </c>
       <c r="G20">
-        <v>289353.04313067364</v>
+        <v>45139.752267445168</v>
       </c>
       <c r="H20">
-        <v>291948.99999999988</v>
+        <v>45826.000000000007</v>
       </c>
       <c r="I20">
-        <v>294393.32592767826</v>
+        <v>46243.907988985615</v>
       </c>
       <c r="J20">
-        <v>296858.11683122808</v>
+        <v>46665.627069649709</v>
       </c>
       <c r="K20">
-        <v>299343.54405246302</v>
+        <v>47091.191997058384</v>
       </c>
       <c r="L20">
-        <v>301849.78036774596</v>
+        <v>47520.637843224889</v>
       </c>
       <c r="M20">
-        <v>304376.99999999983</v>
+        <v>47953.999999999993</v>
       </c>
       <c r="N20">
-        <v>306262.1048140155</v>
+        <v>48282.858476875081</v>
       </c>
       <c r="O20">
-        <v>308158.88468941813</v>
+        <v>48613.972196228628</v>
       </c>
       <c r="P20">
-        <v>310067.41193362407</v>
+        <v>48947.35662404068</v>
       </c>
       <c r="Q20">
-        <v>311987.75930187269</v>
+        <v>49283.027332353711</v>
       </c>
       <c r="R20">
-        <v>313919.99999999994</v>
+        <v>49621.000000000007</v>
       </c>
       <c r="S20">
-        <v>315412.53973250318</v>
+        <v>50032.517552737394</v>
       </c>
       <c r="T20">
-        <v>316912.17577888601</v>
+        <v>50447.447908445523</v>
       </c>
       <c r="U20">
-        <v>318418.94187873317</v>
+        <v>50865.819370228448</v>
       </c>
       <c r="V20">
-        <v>319932.87193204497</v>
+        <v>51287.660475913915</v>
       </c>
       <c r="W20">
-        <v>321454</v>
+        <v>51712.999999999978</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -1925,70 +1934,70 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>380150</v>
+        <v>13959</v>
       </c>
       <c r="D21">
-        <v>372785.53803222271</v>
+        <v>14272.407236899631</v>
       </c>
       <c r="E21">
-        <v>365563.74422194861</v>
+        <v>14592.851087893472</v>
       </c>
       <c r="F21">
-        <v>358481.8547280099</v>
+        <v>14920.489538924669</v>
       </c>
       <c r="G21">
-        <v>351537.15925179608</v>
+        <v>15255.484123034148</v>
       </c>
       <c r="H21">
-        <v>344726.99999999988</v>
+        <v>15598</v>
       </c>
       <c r="I21">
-        <v>343542.0821997759</v>
+        <v>15625.502841239932</v>
       </c>
       <c r="J21">
-        <v>342361.23727517016</v>
+        <v>15653.054176278829</v>
       </c>
       <c r="K21">
-        <v>341184.45122663293</v>
+        <v>15680.654090622351</v>
       </c>
       <c r="L21">
-        <v>340011.71010273451</v>
+        <v>15708.302669926919</v>
       </c>
       <c r="M21">
-        <v>338843</v>
+        <v>15735.999999999993</v>
       </c>
       <c r="N21">
-        <v>337316.50809140125</v>
+        <v>15694.582550061106</v>
       </c>
       <c r="O21">
-        <v>335796.89304774295</v>
+        <v>15653.274111634633</v>
       </c>
       <c r="P21">
-        <v>334284.12388866348</v>
+        <v>15612.074397800216</v>
       </c>
       <c r="Q21">
-        <v>332778.16977336805</v>
+        <v>15570.983122392669</v>
       </c>
       <c r="R21">
-        <v>331279.00000000006</v>
+        <v>15529.999999999998</v>
       </c>
       <c r="S21">
-        <v>329865.99756063061</v>
+        <v>15533.59833213206</v>
       </c>
       <c r="T21">
-        <v>328459.02199254994</v>
+        <v>15537.197498004889</v>
       </c>
       <c r="U21">
-        <v>327058.04758937808</v>
+        <v>15540.797497811665</v>
       </c>
       <c r="V21">
-        <v>325663.04875438043</v>
+        <v>15544.398331745613</v>
       </c>
       <c r="W21">
-        <v>324273.99999999994</v>
+        <v>15548.000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -1996,70 +2005,70 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>368538</v>
+        <v>17698</v>
       </c>
       <c r="D22">
-        <v>364847.00435304135</v>
+        <v>17584.144473479555</v>
       </c>
       <c r="E22">
-        <v>361192.97490459104</v>
+        <v>17471.021407176038</v>
       </c>
       <c r="F22">
-        <v>357575.54142938659</v>
+        <v>17358.626088995225</v>
       </c>
       <c r="G22">
-        <v>353994.33741005952</v>
+        <v>17246.953837156932</v>
       </c>
       <c r="H22">
-        <v>350448.99999999994</v>
+        <v>17136.000000000004</v>
       </c>
       <c r="I22">
-        <v>347846.43063871667</v>
+        <v>17209.565641104378</v>
       </c>
       <c r="J22">
-        <v>345263.18896072044</v>
+        <v>17283.44710291085</v>
       </c>
       <c r="K22">
-        <v>342699.131431185</v>
+        <v>17357.645741252309</v>
       </c>
       <c r="L22">
-        <v>340154.11558122904</v>
+        <v>17432.162917782298</v>
       </c>
       <c r="M22">
-        <v>337628</v>
+        <v>17507.000000000004</v>
       </c>
       <c r="N22">
-        <v>337883.61266648379</v>
+        <v>17637.053351366005</v>
       </c>
       <c r="O22">
-        <v>338139.41885315924</v>
+        <v>17768.072823380979</v>
       </c>
       <c r="P22">
-        <v>338395.41870653734</v>
+        <v>17900.065593015748</v>
       </c>
       <c r="Q22">
-        <v>338651.61237324</v>
+        <v>18033.03889055633</v>
       </c>
       <c r="R22">
-        <v>338908.00000000012</v>
+        <v>18167</v>
       </c>
       <c r="S22">
-        <v>340319.98542796518</v>
+        <v>18237.845294587249</v>
       </c>
       <c r="T22">
-        <v>341737.85358176974</v>
+        <v>18308.966862404264</v>
       </c>
       <c r="U22">
-        <v>343161.62897049339</v>
+        <v>18380.365780825316</v>
       </c>
       <c r="V22">
-        <v>344591.33620532736</v>
+        <v>18452.043131426075</v>
       </c>
       <c r="W22">
-        <v>346027.00000000012</v>
+        <v>18524</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2067,70 +2076,70 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>139266</v>
+        <v>4115</v>
       </c>
       <c r="D23">
-        <v>141899.12936406225</v>
+        <v>4271.6160233797746</v>
       </c>
       <c r="E23">
-        <v>144582.04381743478</v>
+        <v>4434.1928192454043</v>
       </c>
       <c r="F23">
-        <v>147315.6846564897</v>
+        <v>4602.9572533278742</v>
       </c>
       <c r="G23">
-        <v>150101.01097487277</v>
+        <v>4778.1448258195633</v>
       </c>
       <c r="H23">
-        <v>152939</v>
+        <v>4960.0000000000018</v>
       </c>
       <c r="I23">
-        <v>154891.31577143734</v>
+        <v>5127.8488423883982</v>
       </c>
       <c r="J23">
-        <v>156868.55348476919</v>
+        <v>5301.3777722548457</v>
       </c>
       <c r="K23">
-        <v>158871.03127663967</v>
+        <v>5480.7790065565714</v>
       </c>
       <c r="L23">
-        <v>160899.07134480999</v>
+        <v>5666.2512669672878</v>
       </c>
       <c r="M23">
-        <v>162952.99999999994</v>
+        <v>5858</v>
       </c>
       <c r="N23">
-        <v>163649.02859105601</v>
+        <v>6031.0672805559789</v>
       </c>
       <c r="O23">
-        <v>164348.03016082101</v>
+        <v>6209.2476173767309</v>
       </c>
       <c r="P23">
-        <v>165050.01740791477</v>
+        <v>6392.6920693122174</v>
       </c>
       <c r="Q23">
-        <v>165755.00308519718</v>
+        <v>6581.5561580571193</v>
       </c>
       <c r="R23">
-        <v>166463.00000000006</v>
+        <v>6776.0000000000009</v>
       </c>
       <c r="S23">
-        <v>167466.03912284257</v>
+        <v>6952.5563710610741</v>
       </c>
       <c r="T23">
-        <v>168475.12215623556</v>
+        <v>7133.7131187694704</v>
       </c>
       <c r="U23">
-        <v>169490.28551835439</v>
+        <v>7319.5901111603662</v>
       </c>
       <c r="V23">
-        <v>170511.56584681576</v>
+        <v>7510.3103395666521</v>
       </c>
       <c r="W23">
-        <v>171538.99999999997</v>
+        <v>7705.9999999999973</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -2138,70 +2147,70 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C24">
-        <v>34910</v>
+        <v>40321</v>
       </c>
       <c r="D24">
-        <v>35692.706569583257</v>
+        <v>40672.613885919782</v>
       </c>
       <c r="E24">
-        <v>36492.961966839641</v>
+        <v>41027.293973689011</v>
       </c>
       <c r="F24">
-        <v>37311.159648735869</v>
+        <v>41385.06700171069</v>
       </c>
       <c r="G24">
-        <v>38147.701893818521</v>
+        <v>41745.959941556473</v>
       </c>
       <c r="H24">
-        <v>39003</v>
+        <v>42110.000000000015</v>
       </c>
       <c r="I24">
-        <v>39771.141987117437</v>
+        <v>42355.715672230348</v>
       </c>
       <c r="J24">
-        <v>40554.412095465872</v>
+        <v>42602.865117711219</v>
       </c>
       <c r="K24">
-        <v>41353.108264821836</v>
+        <v>42851.456702639669</v>
       </c>
       <c r="L24">
-        <v>42167.534302716944</v>
+        <v>43101.498842030283</v>
       </c>
       <c r="M24">
-        <v>42998.000000000015</v>
+        <v>43353.000000000007</v>
       </c>
       <c r="N24">
-        <v>43759.356019157734</v>
+        <v>43413.033505595638</v>
       </c>
       <c r="O24">
-        <v>44534.19319994875</v>
+        <v>43473.150143195846</v>
       </c>
       <c r="P24">
-        <v>45322.75025030259</v>
+        <v>43533.35002791851</v>
       </c>
       <c r="Q24">
-        <v>46125.270104897005</v>
+        <v>43593.63327504092</v>
       </c>
       <c r="R24">
-        <v>46942.000000000022</v>
+        <v>43654.000000000007</v>
       </c>
       <c r="S24">
-        <v>47702.177469643822</v>
+        <v>43807.31925151094</v>
       </c>
       <c r="T24">
-        <v>48474.665232529391</v>
+        <v>43961.176982723257</v>
       </c>
       <c r="U24">
-        <v>49259.662641210227</v>
+        <v>44115.575084856646</v>
       </c>
       <c r="V24">
-        <v>50057.372276549657</v>
+        <v>44270.515455773057</v>
       </c>
       <c r="W24">
-        <v>50868.000000000007</v>
+        <v>44425.999999999993</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -2209,70 +2218,70 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>110096</v>
+        <v>1142</v>
       </c>
       <c r="D25">
-        <v>110310.16516445472</v>
+        <v>1196.5364559879768</v>
       </c>
       <c r="E25">
-        <v>110524.74693548612</v>
+        <v>1253.6773121788681</v>
       </c>
       <c r="F25">
-        <v>110739.74612350162</v>
+        <v>1313.5469422653546</v>
       </c>
       <c r="G25">
-        <v>110955.16354048511</v>
+        <v>1376.2756594326013</v>
       </c>
       <c r="H25">
-        <v>111170.99999999997</v>
+        <v>1442.0000000000002</v>
       </c>
       <c r="I25">
-        <v>111012.95125132165</v>
+        <v>1503.8599650177623</v>
       </c>
       <c r="J25">
-        <v>110855.1271961961</v>
+        <v>1568.3736438163837</v>
       </c>
       <c r="K25">
-        <v>110697.52751518272</v>
+        <v>1635.6548773401437</v>
       </c>
       <c r="L25">
-        <v>110540.15188929501</v>
+        <v>1705.8223901649658</v>
       </c>
       <c r="M25">
-        <v>110382.99999999999</v>
+        <v>1779.0000000000007</v>
       </c>
       <c r="N25">
-        <v>110654.06542634702</v>
+        <v>1839.0122298883912</v>
       </c>
       <c r="O25">
-        <v>110925.796502888</v>
+        <v>1901.048893580142</v>
       </c>
       <c r="P25">
-        <v>111198.19486424743</v>
+        <v>1965.1782826923416</v>
       </c>
       <c r="Q25">
-        <v>111471.2621490639</v>
+        <v>2031.4709925701416</v>
       </c>
       <c r="R25">
-        <v>111744.99999999997</v>
+        <v>2099.9999999999995</v>
       </c>
       <c r="S25">
-        <v>112473.24593186597</v>
+        <v>2151.9639090561727</v>
       </c>
       <c r="T25">
-        <v>113206.23786701869</v>
+        <v>2205.2136504192017</v>
       </c>
       <c r="U25">
-        <v>113944.00673532159</v>
+        <v>2259.7810416476846</v>
       </c>
       <c r="V25">
-        <v>114686.58366820902</v>
+        <v>2315.698687616753</v>
       </c>
       <c r="W25">
-        <v>115433.99999999996</v>
+        <v>2372.9999999999986</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -2283,67 +2292,67 @@
         <v>26</v>
       </c>
       <c r="C26">
-        <v>168478</v>
+        <v>3433</v>
       </c>
       <c r="D26">
-        <v>171623.34493478888</v>
+        <v>3460.7478070694078</v>
       </c>
       <c r="E26">
-        <v>174827.4108584238</v>
+        <v>3488.7198905143359</v>
       </c>
       <c r="F26">
-        <v>178091.29404320638</v>
+        <v>3516.9180630867791</v>
       </c>
       <c r="G26">
-        <v>181416.11122793553</v>
+        <v>3545.3441521906088</v>
       </c>
       <c r="H26">
-        <v>184803.00000000003</v>
+        <v>3573.9999999999995</v>
       </c>
       <c r="I26">
-        <v>187986.04556815172</v>
+        <v>3601.959120508463</v>
       </c>
       <c r="J26">
-        <v>191223.91589071183</v>
+        <v>3630.1369630145773</v>
       </c>
       <c r="K26">
-        <v>194517.55526886342</v>
+        <v>3658.5352385633041</v>
       </c>
       <c r="L26">
-        <v>197867.92426842655</v>
+        <v>3687.1556715849742</v>
       </c>
       <c r="M26">
-        <v>201276.00000000015</v>
+        <v>3716.0000000000014</v>
       </c>
       <c r="N26">
-        <v>204501.17256190453</v>
+        <v>3750.7441882246976</v>
       </c>
       <c r="O26">
-        <v>207778.02410219726</v>
+        <v>3785.8132307592427</v>
       </c>
       <c r="P26">
-        <v>211107.38270581194</v>
+        <v>3821.2101649554352</v>
       </c>
       <c r="Q26">
-        <v>214490.08972661057</v>
+        <v>3856.9380565639767</v>
       </c>
       <c r="R26">
-        <v>217926.99999999988</v>
+        <v>3892.9999999999991</v>
       </c>
       <c r="S26">
-        <v>221178.51498807347</v>
+        <v>3930.0866256178251</v>
       </c>
       <c r="T26">
-        <v>224478.54323846719</v>
+        <v>3967.5265566041876</v>
       </c>
       <c r="U26">
-        <v>227827.80857888289</v>
+        <v>4005.3231587191526</v>
       </c>
       <c r="V26">
-        <v>231227.04563667823</v>
+        <v>4043.4798297866641</v>
       </c>
       <c r="W26">
-        <v>234676.99999999991</v>
+        <v>4082.0000000000023</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -2354,67 +2363,67 @@
         <v>27</v>
       </c>
       <c r="C27">
-        <v>108508</v>
+        <v>3030</v>
       </c>
       <c r="D27">
-        <v>110157.48267566472</v>
+        <v>3032.3962070292396</v>
       </c>
       <c r="E27">
-        <v>111832.03993658876</v>
+        <v>3034.7943090446597</v>
       </c>
       <c r="F27">
-        <v>113532.05295369025</v>
+        <v>3037.1943075448676</v>
       </c>
       <c r="G27">
-        <v>115257.90869225111</v>
+        <v>3039.5962040296549</v>
       </c>
       <c r="H27">
-        <v>117009.99999999997</v>
+        <v>3042</v>
       </c>
       <c r="I27">
-        <v>118789.63644696819</v>
+        <v>3044.3962219563464</v>
       </c>
       <c r="J27">
-        <v>120596.33986157484</v>
+        <v>3046.794331447099</v>
       </c>
       <c r="K27">
-        <v>122430.52191258434</v>
+        <v>3049.1943299590926</v>
       </c>
       <c r="L27">
-        <v>124292.6005299416</v>
+        <v>3051.5962189803336</v>
       </c>
       <c r="M27">
-        <v>126183.00000000007</v>
+        <v>3053.9999999999995</v>
       </c>
       <c r="N27">
-        <v>127838.96183736601</v>
+        <v>3055.598326140283</v>
       </c>
       <c r="O27">
-        <v>129516.65567988969</v>
+        <v>3057.1974887725273</v>
       </c>
       <c r="P27">
-        <v>131216.36672740933</v>
+        <v>3058.7974883345155</v>
       </c>
       <c r="Q27">
-        <v>132938.3839225815</v>
+        <v>3060.3983252642593</v>
       </c>
       <c r="R27">
-        <v>134683.00000000006</v>
+        <v>3061.9999999999986</v>
       </c>
       <c r="S27">
-        <v>136083.18277985489</v>
+        <v>3063.9973924364081</v>
       </c>
       <c r="T27">
-        <v>137497.92205026167</v>
+        <v>3065.9960878044117</v>
       </c>
       <c r="U27">
-        <v>138927.36914247528</v>
+        <v>3067.9960869539341</v>
       </c>
       <c r="V27">
-        <v>140371.67696101093</v>
+        <v>3069.9973907354533</v>
       </c>
       <c r="W27">
-        <v>141830.99999999997</v>
+        <v>3072.0000000000018</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -2425,67 +2434,280 @@
         <v>28</v>
       </c>
       <c r="C28">
-        <v>165172</v>
+        <v>7531</v>
       </c>
       <c r="D28">
-        <v>165137.78582850515</v>
+        <v>7868.385652669177</v>
       </c>
       <c r="E28">
-        <v>165103.57874422564</v>
+        <v>8220.8860415788276</v>
       </c>
       <c r="F28">
-        <v>165069.37874569339</v>
+        <v>8589.1783005958241</v>
       </c>
       <c r="G28">
-        <v>165035.18583144067</v>
+        <v>8973.9698989012886</v>
       </c>
       <c r="H28">
-        <v>165001</v>
+        <v>9375.9999999999945</v>
       </c>
       <c r="I28">
-        <v>165001</v>
+        <v>9647.2452575636398</v>
       </c>
       <c r="J28">
-        <v>165001</v>
+        <v>9926.3375703481379</v>
       </c>
       <c r="K28">
-        <v>165001</v>
+        <v>10213.503951633624</v>
       </c>
       <c r="L28">
-        <v>165001</v>
+        <v>10508.97798213577</v>
       </c>
       <c r="M28">
-        <v>165001</v>
+        <v>10813.000000000002</v>
       </c>
       <c r="N28">
-        <v>165001</v>
+        <v>11011.943524139369</v>
       </c>
       <c r="O28">
-        <v>165001</v>
+        <v>11214.547320709795</v>
       </c>
       <c r="P28">
-        <v>165001</v>
+        <v>11420.878733417621</v>
       </c>
       <c r="Q28">
-        <v>165001</v>
+        <v>11631.006344995767</v>
       </c>
       <c r="R28">
-        <v>165001</v>
+        <v>11845.000000000005</v>
       </c>
       <c r="S28">
-        <v>165001</v>
+        <v>11996.285842379684</v>
       </c>
       <c r="T28">
-        <v>165001</v>
+        <v>12149.503926726826</v>
       </c>
       <c r="U28">
-        <v>165001</v>
+        <v>12304.678931880911</v>
       </c>
       <c r="V28">
-        <v>165001</v>
+        <v>12461.835851882697</v>
       </c>
       <c r="W28">
-        <v>165001</v>
+        <v>12620.999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29">
+        <v>26520</v>
+      </c>
+      <c r="D29">
+        <v>25834.46231657741</v>
+      </c>
+      <c r="E29">
+        <v>25166.645670688467</v>
+      </c>
+      <c r="F29">
+        <v>24516.091976397329</v>
+      </c>
+      <c r="G29">
+        <v>23882.354989215029</v>
+      </c>
+      <c r="H29">
+        <v>23265.000000000004</v>
+      </c>
+      <c r="I29">
+        <v>23058.776280677568</v>
+      </c>
+      <c r="J29">
+        <v>22854.380552862171</v>
+      </c>
+      <c r="K29">
+        <v>22651.796613020284</v>
+      </c>
+      <c r="L29">
+        <v>22451.008401248422</v>
+      </c>
+      <c r="M29">
+        <v>22251.999999999996</v>
+      </c>
+      <c r="N29">
+        <v>22192.684617235784</v>
+      </c>
+      <c r="O29">
+        <v>22133.527346759562</v>
+      </c>
+      <c r="P29">
+        <v>22074.527767104013</v>
+      </c>
+      <c r="Q29">
+        <v>22015.685457925283</v>
+      </c>
+      <c r="R29">
+        <v>21957</v>
+      </c>
+      <c r="S29">
+        <v>21968.787337438378</v>
+      </c>
+      <c r="T29">
+        <v>21980.581002759613</v>
+      </c>
+      <c r="U29">
+        <v>21992.380999360747</v>
+      </c>
+      <c r="V29">
+        <v>22004.187330640649</v>
+      </c>
+      <c r="W29">
+        <v>22016.000000000011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30">
+        <v>18046</v>
+      </c>
+      <c r="D30">
+        <v>18588.222219199528</v>
+      </c>
+      <c r="E30">
+        <v>19146.736410857979</v>
+      </c>
+      <c r="F30">
+        <v>19722.032094506645</v>
+      </c>
+      <c r="G30">
+        <v>20314.613498108982</v>
+      </c>
+      <c r="H30">
+        <v>20925.000000000004</v>
+      </c>
+      <c r="I30">
+        <v>21274.339314377801</v>
+      </c>
+      <c r="J30">
+        <v>21629.510789165161</v>
+      </c>
+      <c r="K30">
+        <v>21990.611791287705</v>
+      </c>
+      <c r="L30">
+        <v>22357.741313195322</v>
+      </c>
+      <c r="M30">
+        <v>22731.000000000004</v>
+      </c>
+      <c r="N30">
+        <v>23003.202255525885</v>
+      </c>
+      <c r="O30">
+        <v>23278.664115464831</v>
+      </c>
+      <c r="P30">
+        <v>23557.42461336897</v>
+      </c>
+      <c r="Q30">
+        <v>23839.523250214686</v>
+      </c>
+      <c r="R30">
+        <v>24125.000000000007</v>
+      </c>
+      <c r="S30">
+        <v>24342.637687385974</v>
+      </c>
+      <c r="T30">
+        <v>24562.238739040164</v>
+      </c>
+      <c r="U30">
+        <v>24783.820866965008</v>
+      </c>
+      <c r="V30">
+        <v>25007.40194294737</v>
+      </c>
+      <c r="W30">
+        <v>25232.999999999993</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31">
+        <v>68664</v>
+      </c>
+      <c r="D31">
+        <v>68635.977136185596</v>
+      </c>
+      <c r="E31">
+        <v>68607.965708944888</v>
+      </c>
+      <c r="F31">
+        <v>68579.965713610436</v>
+      </c>
+      <c r="G31">
+        <v>68551.977145516692</v>
+      </c>
+      <c r="H31">
+        <v>68524.000000000015</v>
+      </c>
+      <c r="I31">
+        <v>68368.89946330736</v>
+      </c>
+      <c r="J31">
+        <v>68214.149988673016</v>
+      </c>
+      <c r="K31">
+        <v>68059.750781486116</v>
+      </c>
+      <c r="L31">
+        <v>67905.701048934381</v>
+      </c>
+      <c r="M31">
+        <v>67752</v>
+      </c>
+      <c r="N31">
+        <v>67621.296681039137</v>
+      </c>
+      <c r="O31">
+        <v>67490.845507514387</v>
+      </c>
+      <c r="P31">
+        <v>67360.645993001061</v>
+      </c>
+      <c r="Q31">
+        <v>67230.697652012852</v>
+      </c>
+      <c r="R31">
+        <v>67101.000000000029</v>
+      </c>
+      <c r="S31">
+        <v>67009.148883412956</v>
+      </c>
+      <c r="T31">
+        <v>66917.423497107404</v>
+      </c>
+      <c r="U31">
+        <v>66825.823668977609</v>
+      </c>
+      <c r="V31">
+        <v>66734.349227153434</v>
+      </c>
+      <c r="W31">
+        <v>66642.999999999985</v>
       </c>
     </row>
   </sheetData>
